--- a/documents/originals/www.ipa.go.jp/security/scs/rcu1hd0000007a2i-att/SCS-400-criteria-v1.1.xlsx
+++ b/documents/originals/www.ipa.go.jp/security/scs/rcu1hd0000007a2i-att/SCS-400-criteria-v1.1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{827B0EFE-4D06-43BF-A8D5-74658C6FC958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F771A8-F973-4A47-A1AA-70407CAF3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="★3・★4要求事項・評価基準" sheetId="17" r:id="rId1"/>
@@ -3618,96 +3618,95 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>社内ルール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>脆弱性の管理体制</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1-1-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3-2-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サイバーセキュリティサプライチェーンリスクマネジメント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リスクアセスメント</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>データセキュリティ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プラットフォームセキュリティ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ガバナンスの整備</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取引先管理</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リスクの特定</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>攻撃等の防御</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4-3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4-4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>統治(GV)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>防御(PR)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>★3・★4要求事項・評価基準(Ver.1.1:2026年10月28日）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>・情報機器、OS及びソフトウェアについて、以下の状態とすること。
 ‒ライセンスが付与され、サポートされている。
 ‒サポートが終了した場合に削除されるか、又はインターネットとの全てのトラフィックを遮断することで適用範囲から削除される。
-‒やむを得ず、サポートが終了したものを利用する場合、脆弱性悪用のリスクを軽減する対策を実施している。
+‒やむを得ず、サポートが終了したものを利用する場合、脆弱性悪用のリスクを低減する対策を実施している。
 ‒可能であれば、自動アップデートが有効化されている。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>社内ルール</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>脆弱性の管理体制</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1-1-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>3-2-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>サイバーセキュリティサプライチェーンリスクマネジメント</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>リスクアセスメント</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>データセキュリティ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>プラットフォームセキュリティ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ガバナンスの整備</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>取引先管理</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2-1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>リスクの特定</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>3-2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>攻撃等の防御</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>4-3</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>4-4</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>統治(GV)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>防御(PR)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>★3・★4要求事項・評価基準(Ver.1.1:2026年10月28日）</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4495,7 +4494,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="39" x14ac:dyDescent="0.4">
@@ -4544,25 +4543,25 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>511</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>512</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G3" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>502</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>503</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>498</v>
@@ -4577,7 +4576,7 @@
         <v>22</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P3" s="45"/>
     </row>
@@ -4598,7 +4597,7 @@
         <v>16</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H4" s="25" t="s">
         <v>17</v>
@@ -4640,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H5" s="25" t="s">
         <v>17</v>
@@ -4808,7 +4807,7 @@
         <v>31</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H9" s="25" t="s">
         <v>17</v>
@@ -4850,7 +4849,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>17</v>
@@ -4892,7 +4891,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H11" s="25" t="s">
         <v>17</v>
@@ -5018,7 +5017,7 @@
         <v>50</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H14" s="25" t="s">
         <v>17</v>
@@ -5060,7 +5059,7 @@
         <v>50</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H15" s="25" t="s">
         <v>17</v>
@@ -5228,7 +5227,7 @@
         <v>63</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H19" s="26" t="s">
         <v>17</v>
@@ -5270,7 +5269,7 @@
         <v>76</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>17</v>
@@ -5312,7 +5311,7 @@
         <v>76</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H21" s="25" t="s">
         <v>17</v>
@@ -5438,7 +5437,7 @@
         <v>86</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H24" s="25" t="s">
         <v>17</v>
@@ -5468,13 +5467,13 @@
         <v>2</v>
       </c>
       <c r="C25" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="D25" s="37" t="s">
         <v>513</v>
       </c>
-      <c r="D25" s="37" t="s">
-        <v>514</v>
-      </c>
       <c r="E25" s="37" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>95</v>
@@ -5501,7 +5500,7 @@
         <v>100</v>
       </c>
       <c r="N25" s="37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P25" s="45"/>
     </row>
@@ -5510,19 +5509,19 @@
         <v>2</v>
       </c>
       <c r="C26" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>513</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>514</v>
-      </c>
       <c r="E26" s="37" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>101</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>96</v>
@@ -5543,7 +5542,7 @@
         <v>105</v>
       </c>
       <c r="N26" s="37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P26" s="45"/>
     </row>
@@ -5552,13 +5551,13 @@
         <v>2</v>
       </c>
       <c r="C27" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="D27" s="37" t="s">
         <v>513</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>514</v>
-      </c>
       <c r="E27" s="37" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>106</v>
@@ -5585,7 +5584,7 @@
         <v>110</v>
       </c>
       <c r="N27" s="37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P27" s="45"/>
     </row>
@@ -5594,19 +5593,19 @@
         <v>2</v>
       </c>
       <c r="C28" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="D28" s="37" t="s">
         <v>513</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>514</v>
-      </c>
       <c r="E28" s="37" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>111</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>96</v>
@@ -5627,7 +5626,7 @@
         <v>115</v>
       </c>
       <c r="N28" s="37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P28" s="45"/>
     </row>
@@ -5816,7 +5815,7 @@
         <v>119</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H33" s="28" t="s">
         <v>17</v>
@@ -5858,7 +5857,7 @@
         <v>119</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H34" s="28" t="s">
         <v>17</v>
@@ -5900,7 +5899,7 @@
         <v>119</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H35" s="28" t="s">
         <v>17</v>
@@ -6026,7 +6025,7 @@
         <v>138</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H38" s="29" t="s">
         <v>17</v>
@@ -6068,7 +6067,7 @@
         <v>138</v>
       </c>
       <c r="G39" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H39" s="29" t="s">
         <v>17</v>
@@ -6320,7 +6319,7 @@
         <v>156</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H45" s="29" t="s">
         <v>17</v>
@@ -6362,7 +6361,7 @@
         <v>156</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>17</v>
@@ -6404,7 +6403,7 @@
         <v>156</v>
       </c>
       <c r="G47" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>17</v>
@@ -6446,7 +6445,7 @@
         <v>156</v>
       </c>
       <c r="G48" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H48" s="29" t="s">
         <v>17</v>
@@ -6488,7 +6487,7 @@
         <v>156</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H49" s="29" t="s">
         <v>17</v>
@@ -6530,7 +6529,7 @@
         <v>175</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>17</v>
@@ -6572,7 +6571,7 @@
         <v>175</v>
       </c>
       <c r="G51" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H51" s="29" t="s">
         <v>17</v>
@@ -6614,7 +6613,7 @@
         <v>175</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H52" s="29" t="s">
         <v>17</v>
@@ -6644,25 +6643,25 @@
         <v>3</v>
       </c>
       <c r="C53" s="38" t="s">
+        <v>514</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>515</v>
       </c>
-      <c r="D53" s="14" t="s">
-        <v>516</v>
-      </c>
       <c r="E53" s="14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H53" s="13" t="s">
         <v>17</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>188</v>
@@ -6698,7 +6697,7 @@
         <v>186</v>
       </c>
       <c r="G54" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H54" s="29" t="s">
         <v>17</v>
@@ -6740,7 +6739,7 @@
         <v>186</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H55" s="29" t="s">
         <v>17</v>
@@ -6782,7 +6781,7 @@
         <v>186</v>
       </c>
       <c r="G56" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H56" s="29" t="s">
         <v>17</v>
@@ -6824,7 +6823,7 @@
         <v>186</v>
       </c>
       <c r="G57" s="29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H57" s="29" t="s">
         <v>17</v>
@@ -7538,7 +7537,7 @@
         <v>234</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H74" s="27" t="s">
         <v>17</v>
@@ -8042,7 +8041,7 @@
         <v>276</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H86" s="27" t="s">
         <v>17</v>
@@ -8084,7 +8083,7 @@
         <v>276</v>
       </c>
       <c r="G87" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H87" s="27" t="s">
         <v>17</v>
@@ -8126,7 +8125,7 @@
         <v>276</v>
       </c>
       <c r="G88" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H88" s="27" t="s">
         <v>17</v>
@@ -8168,7 +8167,7 @@
         <v>276</v>
       </c>
       <c r="G89" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H89" s="27" t="s">
         <v>17</v>
@@ -8210,7 +8209,7 @@
         <v>276</v>
       </c>
       <c r="G90" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H90" s="27" t="s">
         <v>17</v>
@@ -8252,7 +8251,7 @@
         <v>291</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H91" s="17" t="s">
         <v>17</v>
@@ -8294,7 +8293,7 @@
         <v>291</v>
       </c>
       <c r="G92" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H92" s="27" t="s">
         <v>17</v>
@@ -8336,7 +8335,7 @@
         <v>291</v>
       </c>
       <c r="G93" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H93" s="27" t="s">
         <v>17</v>
@@ -8378,7 +8377,7 @@
         <v>291</v>
       </c>
       <c r="G94" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H94" s="27" t="s">
         <v>17</v>
@@ -8420,7 +8419,7 @@
         <v>302</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H95" s="17" t="s">
         <v>17</v>
@@ -8462,7 +8461,7 @@
         <v>302</v>
       </c>
       <c r="G96" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H96" s="27" t="s">
         <v>17</v>
@@ -8504,7 +8503,7 @@
         <v>302</v>
       </c>
       <c r="G97" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H97" s="27" t="s">
         <v>17</v>
@@ -8546,7 +8545,7 @@
         <v>313</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H98" s="17" t="s">
         <v>17</v>
@@ -8588,7 +8587,7 @@
         <v>313</v>
       </c>
       <c r="G99" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H99" s="27" t="s">
         <v>17</v>
@@ -8630,7 +8629,7 @@
         <v>313</v>
       </c>
       <c r="G100" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H100" s="27" t="s">
         <v>17</v>
@@ -8672,7 +8671,7 @@
         <v>313</v>
       </c>
       <c r="G101" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H101" s="27" t="s">
         <v>17</v>
@@ -8714,7 +8713,7 @@
         <v>313</v>
       </c>
       <c r="G102" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H102" s="27" t="s">
         <v>17</v>
@@ -8882,7 +8881,7 @@
         <v>337</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H106" s="17" t="s">
         <v>17</v>
@@ -8924,7 +8923,7 @@
         <v>337</v>
       </c>
       <c r="G107" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H107" s="27" t="s">
         <v>17</v>
@@ -8954,19 +8953,19 @@
         <v>4</v>
       </c>
       <c r="C108" s="43" t="s">
+        <v>516</v>
+      </c>
+      <c r="D108" s="43" t="s">
         <v>517</v>
       </c>
-      <c r="D108" s="43" t="s">
-        <v>518</v>
-      </c>
       <c r="E108" s="43" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F108" s="10" t="s">
         <v>344</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H108" s="17" t="s">
         <v>96</v>
@@ -8987,7 +8986,7 @@
         <v>348</v>
       </c>
       <c r="N108" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P108" s="45"/>
     </row>
@@ -8996,19 +8995,19 @@
         <v>4</v>
       </c>
       <c r="C109" s="43" t="s">
+        <v>516</v>
+      </c>
+      <c r="D109" s="43" t="s">
         <v>517</v>
       </c>
-      <c r="D109" s="43" t="s">
-        <v>518</v>
-      </c>
       <c r="E109" s="43" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>349</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H109" s="17" t="s">
         <v>17</v>
@@ -9029,7 +9028,7 @@
         <v>353</v>
       </c>
       <c r="N109" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P109" s="45"/>
     </row>
@@ -9302,7 +9301,7 @@
         <v>365</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H116" s="27" t="s">
         <v>17</v>
@@ -9344,7 +9343,7 @@
         <v>365</v>
       </c>
       <c r="G117" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H117" s="27" t="s">
         <v>17</v>
@@ -9386,7 +9385,7 @@
         <v>365</v>
       </c>
       <c r="G118" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H118" s="27" t="s">
         <v>17</v>
@@ -9416,19 +9415,19 @@
         <v>4</v>
       </c>
       <c r="C119" s="43" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D119" s="43" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E119" s="43" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>380</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H119" s="17" t="s">
         <v>96</v>
@@ -9449,7 +9448,7 @@
         <v>500</v>
       </c>
       <c r="N119" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="P119" s="45"/>
     </row>
@@ -9470,7 +9469,7 @@
         <v>384</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H120" s="17" t="s">
         <v>17</v>
@@ -9512,7 +9511,7 @@
         <v>384</v>
       </c>
       <c r="G121" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H121" s="27" t="s">
         <v>17</v>
@@ -9554,7 +9553,7 @@
         <v>384</v>
       </c>
       <c r="G122" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H122" s="27" t="s">
         <v>17</v>
@@ -9614,7 +9613,7 @@
         <v>396</v>
       </c>
       <c r="M123" s="11" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="N123" s="43" t="s">
         <v>208</v>
@@ -9680,7 +9679,7 @@
         <v>393</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H125" s="30" t="s">
         <v>17</v>
@@ -9848,7 +9847,7 @@
         <v>400</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H129" s="27" t="s">
         <v>17</v>
@@ -9890,7 +9889,7 @@
         <v>400</v>
       </c>
       <c r="G130" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H130" s="27" t="s">
         <v>17</v>
@@ -10226,7 +10225,7 @@
         <v>415</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H138" s="27" t="s">
         <v>17</v>
@@ -10268,7 +10267,7 @@
         <v>415</v>
       </c>
       <c r="G139" s="27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H139" s="27" t="s">
         <v>17</v>
@@ -10436,7 +10435,7 @@
         <v>450</v>
       </c>
       <c r="G143" s="19" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H143" s="19" t="s">
         <v>17</v>
@@ -10478,7 +10477,7 @@
         <v>450</v>
       </c>
       <c r="G144" s="31" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H144" s="31" t="s">
         <v>17</v>
@@ -10520,7 +10519,7 @@
         <v>450</v>
       </c>
       <c r="G145" s="31" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H145" s="31" t="s">
         <v>17</v>
@@ -10562,7 +10561,7 @@
         <v>461</v>
       </c>
       <c r="G146" s="19" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H146" s="19" t="s">
         <v>17</v>
@@ -10604,7 +10603,7 @@
         <v>461</v>
       </c>
       <c r="G147" s="31" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H147" s="31" t="s">
         <v>17</v>
@@ -10940,7 +10939,7 @@
         <v>490</v>
       </c>
       <c r="G155" s="23" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H155" s="33" t="s">
         <v>17</v>
@@ -10976,7 +10975,7 @@
       <c r="M158" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" autoFilter="0" pivotTables="0"/>
+  <sheetProtection sheet="1" autoFilter="0" pivotTables="0"/>
   <autoFilter ref="B2:N155" xr:uid="{1A0C9EE9-850D-48C0-B8E4-8EAD6C85187B}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="B3:F155">
@@ -11038,271 +11037,6 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b8d57d52-3360-457f-a90d-051d484a5a03">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b362d10-ed65-451c-8ba9-46a6a014d10c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100D569F24C4ACBB646A8475C8FB912F125" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f446f17e8bcc42938f888a15f2f3741b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b8d57d52-3360-457f-a90d-051d484a5a03" xmlns:ns3="7b362d10-ed65-451c-8ba9-46a6a014d10c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="367e069007342ac44cb8ae84ad5e05b0" ns2:_="" ns3:_="">
-    <xsd:import namespace="b8d57d52-3360-457f-a90d-051d484a5a03"/>
-    <xsd:import namespace="7b362d10-ed65-451c-8ba9-46a6a014d10c"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b8d57d52-3360-457f-a90d-051d484a5a03" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f804ebf9-b652-43cc-9369-06696671cd4d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7b362d10-ed65-451c-8ba9-46a6a014d10c" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{0f63fb3a-b6c0-4587-867c-0d3186ec1e46}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="7b362d10-ed65-451c-8ba9-46a6a014d10c">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C29BEEA7-6DBC-4DD6-8B2C-DFB55670D68D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7b362d10-ed65-451c-8ba9-46a6a014d10c"/>
-    <ds:schemaRef ds:uri="b8d57d52-3360-457f-a90d-051d484a5a03"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55680F40-F53B-4ECA-BC55-41F55654AE3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b8d57d52-3360-457f-a90d-051d484a5a03"/>
-    <ds:schemaRef ds:uri="7b362d10-ed65-451c-8ba9-46a6a014d10c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2375786B-9CDD-4F90-A50F-68D101AA498D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f54277c9-dafe-44aa-85a4-73d5c7c52450}" enabled="0" method="" siteId="{f54277c9-dafe-44aa-85a4-73d5c7c52450}" removed="1"/>
